--- a/excel_templates/contact.xlsx
+++ b/excel_templates/contact.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18345" windowHeight="12120"/>
+    <workbookView windowWidth="18330" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="联系单" sheetId="22" r:id="rId1"/>
@@ -338,18 +338,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -704,7 +698,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -728,16 +722,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -746,88 +740,88 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -872,74 +866,95 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="52" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="52" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="52" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="52" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="52" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="52" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1478,125 +1493,125 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="13"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="24"/>
     </row>
     <row r="15" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="13"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="24"/>
     </row>
     <row r="16" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="13" t="s">
+      <c r="B16" s="27"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="13"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="24"/>
     </row>
     <row r="17" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
     </row>
     <row r="18" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="15" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="13"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="24"/>
     </row>
     <row r="19" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
     </row>
     <row r="20" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="13" t="s">
+      <c r="B20" s="27"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="13"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="24"/>
     </row>
     <row r="21" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
     </row>
     <row r="22" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="13" t="s">
+      <c r="B22" s="27"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="24"/>
     </row>
     <row r="23" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
     </row>
     <row r="24" ht="24.95" customHeight="1"/>
     <row r="25" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
     </row>
     <row r="26" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
     </row>
     <row r="27" ht="24.95" customHeight="1"/>
     <row r="28" ht="24.95" customHeight="1"/>

--- a/excel_templates/contact.xlsx
+++ b/excel_templates/contact.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18330" windowHeight="12135"/>
+    <workbookView windowWidth="11730" windowHeight="6930"/>
   </bookViews>
   <sheets>
     <sheet name="联系单" sheetId="22" r:id="rId1"/>
@@ -38,13 +38,13 @@
     <t>代理客户：</t>
   </si>
   <si>
-    <t>{{Proxy client}}</t>
+    <t>{{Proxy_client}}</t>
   </si>
   <si>
     <t>代理合同号：</t>
   </si>
   <si>
-    <t>{{Contract No.}}</t>
+    <t>{{Contract_No.}}</t>
   </si>
   <si>
     <t>时间：</t>
@@ -62,7 +62,7 @@
     <t>报关公司：</t>
   </si>
   <si>
-    <t>{{customs declaration}}</t>
+    <t>{{customs_declaration}}</t>
   </si>
   <si>
     <t>电 话：</t>
@@ -92,7 +92,7 @@
     <t>净重</t>
   </si>
   <si>
-    <t>{{Bill of Lading Number}}</t>
+    <t>{{Bill_of_Lading_Number}}</t>
   </si>
   <si>
     <t>{{commodity}}</t>
@@ -870,7 +870,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -878,9 +878,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="52" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -911,9 +908,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="52" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -927,9 +921,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="52" applyFill="1" applyBorder="1">
@@ -1351,267 +1342,267 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="13"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="13"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="13"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="12"/>
     </row>
     <row r="9" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="13"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="13"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="13"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="12"/>
     </row>
     <row r="12" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="13"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="12"/>
     </row>
     <row r="13" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="13"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="12"/>
     </row>
     <row r="14" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="24"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="21"/>
     </row>
     <row r="15" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="24"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="21"/>
     </row>
     <row r="16" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="24" t="s">
+      <c r="B16" s="24"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="21"/>
     </row>
     <row r="17" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
     </row>
     <row r="18" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="28" t="s">
+      <c r="B18" s="24"/>
+      <c r="C18" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="27"/>
-      <c r="F18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="19" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
     </row>
     <row r="20" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="24" t="s">
+      <c r="B20" s="24"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="21"/>
     </row>
     <row r="21" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="24" t="s">
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" ht="24.95" customHeight="1"/>
     <row r="25" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
     </row>
     <row r="26" ht="24.95" customHeight="1" spans="1:6">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
     </row>
     <row r="27" ht="24.95" customHeight="1"/>
     <row r="28" ht="24.95" customHeight="1"/>

--- a/excel_templates/contact.xlsx
+++ b/excel_templates/contact.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="11730" windowHeight="6930"/>
+    <workbookView windowWidth="18330" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="联系单" sheetId="22" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <t>代理合同号：</t>
   </si>
   <si>
-    <t>{{Contract_No.}}</t>
+    <t>{{Contract_No}}</t>
   </si>
   <si>
     <t>时间：</t>

--- a/excel_templates/contact.xlsx
+++ b/excel_templates/contact.xlsx
@@ -1367,7 +1367,10 @@
       <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="7"/>
+      <c r="F3" s="7">
+        <f ca="1">TODAY()</f>
+        <v>46100</v>
+      </c>
     </row>
     <row r="4" ht="24.95" customHeight="1" spans="1:6">
       <c r="A4" s="8" t="s">
